--- a/mesinblog/articles.xlsx
+++ b/mesinblog/articles.xlsx
@@ -57,10 +57,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -428,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -444,6 +447,7 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,6 +516,11 @@
           <t>related_slugs</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>gambar_cover</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -560,6 +569,7 @@
 Kalau jawabannya cuma profil WhatsApp atau feed Instagram yang isinya campur aduk antara promosi dan story pribadi, ya wajar konversinya rendah.
 ## Halaman yang sebenarnya dibutuhkan
 Untuk kebanyakan usaha kecil, saya selalu mulai dari struktur yang sama: Beranda, Layanan, Tentang Kami, dan Kontak. Masing-masing menjawab keraguan yang berbeda dari calon pembeli.
+gambar: before-after-bakso.jpg | Tampilan sebelum dan sesudah landing page dibenahi
 ## Iklan bukan solusi kalau fondasinya belum ada
 Menambah budget iklan ke halaman yang belum siap itu seperti menuang lebih banyak air ke ember bocor. Yang perlu dibenahi dulu justru embernya.</t>
         </is>
@@ -582,6 +592,11 @@
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>katalog-whatsapp,klinik-gigi-repeat,halaman-kecamatan</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>cover-warung-bakso.jpg</t>
         </is>
       </c>
     </row>
@@ -868,6 +883,11 @@
       <c r="M7" s="2" t="inlineStr">
         <is>
           <t>warung-bakso-4-halaman</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>cover-katalog-whatsapp.jpg</t>
         </is>
       </c>
     </row>
@@ -882,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -891,17 +911,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Kolom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Wajib diisi?</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
@@ -1178,6 +1198,82 @@
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>gambar_cover</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Opsional</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Nama file gambar cover, contoh: 'foto-klinik.jpg'. Muncul di kartu index DAN di atas artikel. File aslinya taruh di folder 'images/' (satu folder sama generate_blog.py).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CARA SISIP GAMBAR DI TENGAH ISI ARTIKEL:</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Di kolom 'isi', taruh baris sendiri (dikasih baris kosong sebelum/sesudahnya) berformat:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>gambar: nama-file.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Atau kalau mau kasih keterangan di bawah gambar:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>gambar: nama-file.jpg | Ini keterangan gambarnya</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Semua file gambar (cover maupun sisipan) ditaruh di folder 'images/' yang sejajar dengan generate_blog.py. Nama file harus persis sama (huruf besar/kecil ikut diperhatikan).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
